--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -910,12 +910,7 @@
         <v>123324684</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>123324684</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>123324684</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>123324684</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>123324684</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>123324684</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,6 +1165,116 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130669607</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lagmansören, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>616647</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6934724</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>130669607</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>130669607</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>130669607</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>130669607</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>131108352</v>
       </c>
       <c r="B8" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>131106420</v>
       </c>
       <c r="B10" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131106423</v>
       </c>
       <c r="B11" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106436</v>
+        <v>131108352</v>
       </c>
       <c r="B7" t="n">
-        <v>5493</v>
+        <v>80219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,43 +1288,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartmyran, Mpd</t>
+          <t>S Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616762</v>
+        <v>616863</v>
       </c>
       <c r="R7" t="n">
-        <v>6934714</v>
+        <v>6934788</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0743</t>
+          <t>2025_0758</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två kläckhål</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131108352</v>
+        <v>131106436</v>
       </c>
       <c r="B8" t="n">
-        <v>80217</v>
+        <v>5493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,43 +1418,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Svartmyran, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616863</v>
+        <v>616762</v>
       </c>
       <c r="R8" t="n">
-        <v>6934788</v>
+        <v>6934714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0758</t>
+          <t>2025_0743</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Två kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,7 +1540,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80255</v>
+        <v>80257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>131106420</v>
       </c>
       <c r="B10" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131106423</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131108352</v>
+        <v>131106436</v>
       </c>
       <c r="B7" t="n">
-        <v>80219</v>
+        <v>5493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,43 +1288,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Svartmyran, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616863</v>
+        <v>616762</v>
       </c>
       <c r="R7" t="n">
-        <v>6934788</v>
+        <v>6934714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0758</t>
+          <t>2025_0743</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Två kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106436</v>
+        <v>131108352</v>
       </c>
       <c r="B8" t="n">
-        <v>5493</v>
+        <v>80220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,43 +1418,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartmyran, Mpd</t>
+          <t>S Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616762</v>
+        <v>616863</v>
       </c>
       <c r="R8" t="n">
-        <v>6934714</v>
+        <v>6934788</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0743</t>
+          <t>2025_0758</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Två kläckhål</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,7 +1540,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80257</v>
+        <v>80258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>131106420</v>
       </c>
       <c r="B10" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131106423</v>
       </c>
       <c r="B11" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106436</v>
+        <v>131108352</v>
       </c>
       <c r="B7" t="n">
-        <v>5493</v>
+        <v>80220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,43 +1288,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartmyran, Mpd</t>
+          <t>S Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616762</v>
+        <v>616863</v>
       </c>
       <c r="R7" t="n">
-        <v>6934714</v>
+        <v>6934788</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0743</t>
+          <t>2025_0758</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två kläckhål</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131108352</v>
+        <v>131106436</v>
       </c>
       <c r="B8" t="n">
-        <v>80220</v>
+        <v>5493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,43 +1418,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Svartmyran, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616863</v>
+        <v>616762</v>
       </c>
       <c r="R8" t="n">
-        <v>6934788</v>
+        <v>6934714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0758</t>
+          <t>2025_0743</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Två kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131108352</v>
       </c>
       <c r="B7" t="n">
-        <v>80220</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80258</v>
+        <v>80259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>131106420</v>
       </c>
       <c r="B10" t="n">
-        <v>80383</v>
+        <v>80384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131106423</v>
       </c>
       <c r="B11" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131108352</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80259</v>
+        <v>80262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>131106420</v>
       </c>
       <c r="B10" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131106423</v>
       </c>
       <c r="B11" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131108352</v>
+        <v>131106436</v>
       </c>
       <c r="B7" t="n">
-        <v>80224</v>
+        <v>5493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,43 +1288,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Svartmyran, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616863</v>
+        <v>616762</v>
       </c>
       <c r="R7" t="n">
-        <v>6934788</v>
+        <v>6934714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0758</t>
+          <t>2025_0743</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Två kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106436</v>
+        <v>131108352</v>
       </c>
       <c r="B8" t="n">
-        <v>5493</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,43 +1418,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartmyran, Mpd</t>
+          <t>S Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616762</v>
+        <v>616863</v>
       </c>
       <c r="R8" t="n">
-        <v>6934714</v>
+        <v>6934788</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0743</t>
+          <t>2025_0758</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Två kläckhål</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,7 +1540,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80262</v>
+        <v>80263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>131106420</v>
       </c>
       <c r="B10" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131106423</v>
       </c>
       <c r="B11" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117866395</v>
+        <v>131108352</v>
       </c>
       <c r="B2" t="n">
-        <v>90468</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stordalen, Mpd</t>
+          <t>S Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616913</v>
+        <v>616863</v>
       </c>
       <c r="R2" t="n">
-        <v>6934771</v>
+        <v>6934788</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,24 +747,34 @@
           <t>Timrå</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2025_0758</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,49 +789,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117866396</v>
+        <v>131106418</v>
       </c>
       <c r="B3" t="n">
-        <v>90468</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,19 +838,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stordalen, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616552</v>
+        <v>616923</v>
       </c>
       <c r="R3" t="n">
-        <v>6934695</v>
+        <v>6934843</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,24 +877,29 @@
           <t>Timrå</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025_0761</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,44 +914,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>David Isaksson, Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324684</v>
+        <v>117866395</v>
       </c>
       <c r="B4" t="n">
-        <v>57681</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,17 +965,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Patronsvedberget, Mpd</t>
+          <t>Stordalen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616589</v>
+        <v>616913</v>
       </c>
       <c r="R4" t="n">
-        <v>6934719</v>
+        <v>6934771</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,34 +997,24 @@
           <t>Timrå</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2024_948</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,31 +1029,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324689</v>
+        <v>117866396</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,24 +1074,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Patronsvedberget, Mpd</t>
+          <t>Stordalen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616664</v>
+        <v>616552</v>
       </c>
       <c r="R5" t="n">
-        <v>6934704</v>
+        <v>6934695</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,34 +1108,24 @@
           <t>Timrå</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2024_946</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,65 +1140,66 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130669607</v>
+        <v>131108158</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lagmansören, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616647</v>
+        <v>616773</v>
       </c>
       <c r="R6" t="n">
-        <v>6934724</v>
+        <v>6934747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,17 +1226,27 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>2025-0741</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,12 +1261,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106436</v>
+        <v>123324679</v>
       </c>
       <c r="B7" t="n">
-        <v>5493</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,43 +1288,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartmyran, Mpd</t>
+          <t>Patronssvedberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616762</v>
+        <v>616540</v>
       </c>
       <c r="R7" t="n">
-        <v>6934714</v>
+        <v>6934737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,32 +1351,32 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0743</t>
+          <t>2024_951</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två kläckhål</t>
+          <t>grenar av levande men mycket gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131108352</v>
+        <v>131108199</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,43 +1418,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Svartmyran, Mpd</t>
+          <t>Svartmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616863</v>
+        <v>616770</v>
       </c>
       <c r="R8" t="n">
-        <v>6934788</v>
+        <v>6934746</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0758</t>
+          <t>2025-0742</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1501,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1521,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,7 +1535,7 @@
         <v>131106422</v>
       </c>
       <c r="B9" t="n">
-        <v>80263</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1667,32 +1662,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106420</v>
+        <v>131106423</v>
       </c>
       <c r="B10" t="n">
-        <v>80388</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1702,7 +1697,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1711,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616876</v>
+        <v>616860</v>
       </c>
       <c r="R10" t="n">
-        <v>6934813</v>
+        <v>6934783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,7 +1736,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0759</t>
+          <t>2025_0756</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1751,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,12 +1756,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1797,32 +1792,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131106423</v>
+        <v>131106420</v>
       </c>
       <c r="B11" t="n">
-        <v>80359</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1832,7 +1827,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1841,10 +1836,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616860</v>
+        <v>616876</v>
       </c>
       <c r="R11" t="n">
-        <v>6934783</v>
+        <v>6934813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1871,7 +1866,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025_0756</t>
+          <t>2025_0759</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1881,7 +1876,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1891,12 +1886,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,6 +1915,501 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123324684</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Patronsvedberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>616589</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6934719</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2024_948</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hackspår</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130669607</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lagmansören, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>616647</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6934724</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131106436</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>616762</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6934714</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2025_0743</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Två kläckhål</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123324689</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Patronsvedberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>616664</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6934704</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2024_946</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 23282-2025 artfynd.xlsx
+++ b/artfynd/A 23282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108352</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866395</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1274,6 +1299,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108158</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324679</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108199</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1659,6 +1699,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106422</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1789,6 +1834,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106423</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1919,6 +1969,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106420</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2044,6 +2099,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324684</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2154,6 +2214,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669607</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2284,6 +2349,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106436</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2414,8 +2484,29 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324689</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>